--- a/docs/column/koyou-hokenryo-ritsu/koyou-table.xlsx
+++ b/docs/column/koyou-hokenryo-ritsu/koyou-table.xlsx
@@ -217,9 +217,10 @@
     <mergeCell ref="A5:E5"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="E7" r:id="rId7"/>
-    <hyperlink ref="E8" r:id="rId8"/>
-    <hyperlink ref="E9" r:id="rId9"/>
+    <hyperlink ref="A4" r:id="rId1"/>
+    <hyperlink ref="E7" r:id="rId2"/>
+    <hyperlink ref="E8" r:id="rId3"/>
+    <hyperlink ref="E9" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="2"/>
